--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260807.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.86%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>46,121,000</t>
+          <t>47,068,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -792,29 +792,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>20,089,000</t>
+          <t>3,816,646,641</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -831,78 +831,78 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>20,089,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -924,90 +924,90 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3,284,309,231</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,174,000</t>
+          <t>9,470,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,448,145,322</t>
+          <t>2,452,825,322</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1271,78 +1271,78 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1371,154 +1371,154 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,951,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>8,951,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1606,51 +1606,51 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1760,51 +1760,29 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>PB_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>PAYABLES</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-50,912,323</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>PB_NTD</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>-16,304,964</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
